--- a/data/merged/2026-09-09/MERGED_IT_Mite-Vacuum_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_IT_Mite-Vacuum_2026-09-09.xlsx
@@ -4464,13 +4464,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4904,13 +4904,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5015,94 +5015,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId35" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Product 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId36" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Product 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId37" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5444,7 +5356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR38"/>
+  <dimension ref="A1:BR36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -9821,7 +9733,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -9834,23 +9746,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO Galleggiante per Lavasciuga Pavimenti Filtro per Serbatoio di Scarico Acciaio Inossidabile Parte Accessori Facile In</t>
+          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F8W81X7Y?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M22" s="14"/>
@@ -9870,9 +9782,13 @@
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22" s="2"/>
-      <c r="AD22" s="19"/>
+      <c r="AD22" s="19">
+        <v>2</v>
+      </c>
       <c r="AE22" s="15"/>
-      <c r="AF22" s="21"/>
+      <c r="AF22" s="21">
+        <v>2.5</v>
+      </c>
       <c r="AG22" s="22">
         <v>0</v>
       </c>
@@ -9923,104 +9839,210 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Yaasier</t>
+        </is>
+      </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.itundefined</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
+          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
-        </is>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="15"/>
+          <t>B0FKRC3KQY</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+        </is>
+      </c>
+      <c r="O23" s="15">
+        <v>782137</v>
+      </c>
       <c r="P23" s="15"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="18"/>
+      <c r="Q23" s="16">
+        <v>0</v>
+      </c>
+      <c r="R23" s="17" t="inlineStr">
+        <is>
+          <t>Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="S23" s="18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="T23" s="15"/>
       <c r="U23" s="16"/>
       <c r="V23" s="15"/>
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="20"/>
+      <c r="Y23" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="20">
+        <v>22.12</v>
+      </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE23" s="15"/>
+        <v>15</v>
+      </c>
+      <c r="AE23" s="15">
+        <v>1</v>
+      </c>
       <c r="AF23" s="21">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
       </c>
-      <c r="AH23" s="20"/>
+      <c r="AH23" s="20">
+        <v>5.12</v>
+      </c>
       <c r="AI23" s="16">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AJ23"/>
-      <c r="AK23" s="13"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="13"/>
+      <c r="AK23" s="13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AL23" s="19">
+        <v>374</v>
+      </c>
+      <c r="AM23" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN23" s="13"/>
       <c r="AO23" s="13"/>
       <c r="AP23"/>
-      <c r="AQ23" s="19"/>
-      <c r="AR23" s="19"/>
-      <c r="AS23" s="14"/>
-      <c r="AT23" s="13"/>
-      <c r="AU23" s="13"/>
-      <c r="AV23" s="14"/>
-      <c r="AW23" s="13"/>
+      <c r="AQ23" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR23" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS23" s="14" t="inlineStr">
+        <is>
+          <t>Renyu</t>
+        </is>
+      </c>
+      <c r="AT23" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU23" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV23" s="14" t="inlineStr">
+        <is>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
+        </is>
+      </c>
+      <c r="AW23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+        </is>
+      </c>
       <c r="AX23" s="13"/>
       <c r="AY23" s="13"/>
       <c r="AZ23" s="13"/>
       <c r="BA23" s="13"/>
       <c r="BB23" s="13"/>
-      <c r="BC23" s="13"/>
+      <c r="BC23" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD23" s="13"/>
       <c r="BE23" s="13"/>
       <c r="BF23" s="13"/>
       <c r="BG23" s="13"/>
       <c r="BH23" s="14"/>
       <c r="BI23" s="23"/>
-      <c r="BJ23" s="23"/>
-      <c r="BK23" s="23"/>
-      <c r="BL23" s="23"/>
-      <c r="BM23" s="23"/>
-      <c r="BN23" s="23"/>
-      <c r="BO23" s="23"/>
-      <c r="BP23" s="23"/>
-      <c r="BQ23" s="23"/>
-      <c r="BR23" s="13"/>
+      <c r="BJ23" s="23" t="inlineStr">
+        <is>
+          <t>400 grammi</t>
+        </is>
+      </c>
+      <c r="BK23" s="23" t="inlineStr">
+        <is>
+          <t>400.00 g</t>
+        </is>
+      </c>
+      <c r="BL23" s="23" t="inlineStr">
+        <is>
+          <t>4 x 4 x 8 cm</t>
+        </is>
+      </c>
+      <c r="BM23" s="23" t="inlineStr">
+        <is>
+          <t>4.00 x 4.00 x 8.00 cm</t>
+        </is>
+      </c>
+      <c r="BN23" s="23" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="BO23" s="23" t="inlineStr">
+        <is>
+          <t>400.00 g</t>
+        </is>
+      </c>
+      <c r="BP23" s="23" t="inlineStr">
+        <is>
+          <t>23.2 x 11.7 x 10.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ23" s="23" t="inlineStr">
+        <is>
+          <t>23.20 x 11.70 x 10.20 cm</t>
+        </is>
+      </c>
+      <c r="BR23" s="13" t="inlineStr">
+        <is>
+          <t>小包裹</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
@@ -10029,40 +10051,40 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspiratore Floreale Delight (Plant Essential Oil)</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -10076,7 +10098,7 @@
         </is>
       </c>
       <c r="O24" s="15">
-        <v>442310</v>
+        <v>487788</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="16">
@@ -10089,7 +10111,7 @@
       </c>
       <c r="S24" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T24" s="15"/>
@@ -10101,37 +10123,37 @@
         <v>1</v>
       </c>
       <c r="Z24" s="20">
-        <v>18.99</v>
+        <v>22.12</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE24" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="21">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
       </c>
       <c r="AH24" s="20">
-        <v>2.81</v>
+        <v>5.12</v>
       </c>
       <c r="AI24" s="16">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="13" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AL24" s="19">
-        <v>408</v>
+        <v>345</v>
       </c>
       <c r="AM24" s="13" t="inlineStr">
         <is>
@@ -10141,13 +10163,15 @@
       <c r="AN24" s="13"/>
       <c r="AO24" s="13"/>
       <c r="AP24"/>
-      <c r="AQ24" s="19"/>
+      <c r="AQ24" s="19">
+        <v>9</v>
+      </c>
       <c r="AR24" s="19">
         <v>1</v>
       </c>
       <c r="AS24" s="14" t="inlineStr">
         <is>
-          <t>tengjidainzi</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT24" s="13" t="inlineStr">
@@ -10162,12 +10186,12 @@
       </c>
       <c r="AV24" s="14" t="inlineStr">
         <is>
-          <t>深圳市 广东 518033 CN</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW24" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1LBASE3VLPMEX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX24" s="13"/>
@@ -10175,7 +10199,11 @@
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="13"/>
+      <c r="BC24" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
       <c r="BF24" s="13"/>
@@ -10184,43 +10212,43 @@
       <c r="BI24" s="23"/>
       <c r="BJ24" s="23" t="inlineStr">
         <is>
-          <t>50 grammi</t>
+          <t>400 grammi</t>
         </is>
       </c>
       <c r="BK24" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL24" s="23" t="inlineStr">
         <is>
-          <t>6L x 1,3l x 8H cm</t>
+          <t>6L x 4l x 8H cm</t>
         </is>
       </c>
       <c r="BM24" s="23"/>
       <c r="BN24" s="23" t="inlineStr">
         <is>
-          <t>50 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BO24" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BP24" s="23" t="inlineStr">
         <is>
-          <t>10 x 6 x 1.5 cm</t>
+          <t>23.4 x 11.9 x 10 cm</t>
         </is>
       </c>
       <c r="BQ24" s="23" t="inlineStr">
         <is>
-          <t>10.00 x 6.00 x 1.50 cm</t>
+          <t>23.40 x 11.90 x 10.00 cm</t>
         </is>
       </c>
       <c r="BR24" s="13" t="inlineStr">
         <is>
-          <t>轻型信封</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -10231,40 +10259,40 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
+          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -10278,11 +10306,13 @@
         </is>
       </c>
       <c r="O25" s="15">
-        <v>782137</v>
-      </c>
-      <c r="P25" s="15"/>
+        <v>879988</v>
+      </c>
+      <c r="P25" s="15">
+        <v>-9826</v>
+      </c>
       <c r="Q25" s="16">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R25" s="17" t="inlineStr">
         <is>
@@ -10291,7 +10321,7 @@
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T25" s="15"/>
@@ -10303,37 +10333,37 @@
         <v>1</v>
       </c>
       <c r="Z25" s="20">
-        <v>22.12</v>
+        <v>131.98</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF25" s="21">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
       </c>
       <c r="AH25" s="20">
-        <v>5.12</v>
+        <v>8.68</v>
       </c>
       <c r="AI25" s="16">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="13" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL25" s="19">
-        <v>374</v>
+        <v>280</v>
       </c>
       <c r="AM25" s="13" t="inlineStr">
         <is>
@@ -10351,7 +10381,7 @@
       </c>
       <c r="AS25" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="AT25" s="13" t="inlineStr">
@@ -10366,12 +10396,12 @@
       </c>
       <c r="AV25" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>郑州市 河南 450000 CN</t>
         </is>
       </c>
       <c r="AW25" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
         </is>
       </c>
       <c r="AX25" s="13"/>
@@ -10392,47 +10422,47 @@
       <c r="BI25" s="23"/>
       <c r="BJ25" s="23" t="inlineStr">
         <is>
-          <t>400 grammi</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BK25" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BL25" s="23" t="inlineStr">
         <is>
-          <t>4 x 4 x 8 cm</t>
+          <t>36 x 29 x 25 cm</t>
         </is>
       </c>
       <c r="BM25" s="23" t="inlineStr">
         <is>
-          <t>4.00 x 4.00 x 8.00 cm</t>
+          <t>36.00 x 29.00 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN25" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>2.6 kg</t>
         </is>
       </c>
       <c r="BO25" s="23" t="inlineStr">
         <is>
-          <t>400.00 g</t>
+          <t>2.60 kg</t>
         </is>
       </c>
       <c r="BP25" s="23" t="inlineStr">
         <is>
-          <t>23.2 x 11.7 x 10.2 cm</t>
+          <t>33.3 x 28.1 x 27.2 cm</t>
         </is>
       </c>
       <c r="BQ25" s="23" t="inlineStr">
         <is>
-          <t>23.20 x 11.70 x 10.20 cm</t>
+          <t>33.30 x 28.10 x 27.20 cm</t>
         </is>
       </c>
       <c r="BR25" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -10443,206 +10473,104 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Yaasier</t>
-        </is>
-      </c>
+      <c r="F26" s="14"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
-        </is>
-      </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N26" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O26" s="15">
-        <v>487788</v>
-      </c>
+          <t>B0FP52HNHM</t>
+        </is>
+      </c>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="15"/>
       <c r="P26" s="15"/>
-      <c r="Q26" s="16">
-        <v>0</v>
-      </c>
-      <c r="R26" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S26" s="18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="18"/>
       <c r="T26" s="15"/>
       <c r="U26" s="16"/>
       <c r="V26" s="15"/>
       <c r="W26" s="15"/>
       <c r="X26" s="15"/>
-      <c r="Y26" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="20">
-        <v>22.12</v>
-      </c>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="20"/>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>13</v>
-      </c>
-      <c r="AE26" s="15">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE26" s="15"/>
       <c r="AF26" s="21">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
-      <c r="AH26" s="20">
-        <v>5.12</v>
-      </c>
+      <c r="AH26" s="20"/>
       <c r="AI26" s="16">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AJ26"/>
-      <c r="AK26" s="13" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AL26" s="19">
-        <v>345</v>
-      </c>
-      <c r="AM26" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK26" s="13"/>
+      <c r="AL26" s="19"/>
+      <c r="AM26" s="13"/>
       <c r="AN26" s="13"/>
       <c r="AO26" s="13"/>
       <c r="AP26"/>
-      <c r="AQ26" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR26" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS26" s="14" t="inlineStr">
-        <is>
-          <t>Renyu</t>
-        </is>
-      </c>
-      <c r="AT26" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU26" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV26" s="14" t="inlineStr">
-        <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
-        </is>
-      </c>
-      <c r="AW26" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
-        </is>
-      </c>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="14"/>
+      <c r="AT26" s="13"/>
+      <c r="AU26" s="13"/>
+      <c r="AV26" s="14"/>
+      <c r="AW26" s="13"/>
       <c r="AX26" s="13"/>
       <c r="AY26" s="13"/>
       <c r="AZ26" s="13"/>
       <c r="BA26" s="13"/>
       <c r="BB26" s="13"/>
-      <c r="BC26" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC26" s="13"/>
       <c r="BD26" s="13"/>
       <c r="BE26" s="13"/>
       <c r="BF26" s="13"/>
       <c r="BG26" s="13"/>
       <c r="BH26" s="14"/>
       <c r="BI26" s="23"/>
-      <c r="BJ26" s="23" t="inlineStr">
-        <is>
-          <t>400 grammi</t>
-        </is>
-      </c>
-      <c r="BK26" s="23" t="inlineStr">
-        <is>
-          <t>400.00 g</t>
-        </is>
-      </c>
-      <c r="BL26" s="23" t="inlineStr">
-        <is>
-          <t>6L x 4l x 8H cm</t>
-        </is>
-      </c>
+      <c r="BJ26" s="23"/>
+      <c r="BK26" s="23"/>
+      <c r="BL26" s="23"/>
       <c r="BM26" s="23"/>
-      <c r="BN26" s="23" t="inlineStr">
-        <is>
-          <t>400 g</t>
-        </is>
-      </c>
-      <c r="BO26" s="23" t="inlineStr">
-        <is>
-          <t>400.00 g</t>
-        </is>
-      </c>
-      <c r="BP26" s="23" t="inlineStr">
-        <is>
-          <t>23.4 x 11.9 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BQ26" s="23" t="inlineStr">
-        <is>
-          <t>23.40 x 11.90 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BR26" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
+      <c r="BN26" s="23"/>
+      <c r="BO26" s="23"/>
+      <c r="BP26" s="23"/>
+      <c r="BQ26" s="23"/>
+      <c r="BR26" s="13"/>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
@@ -10651,40 +10579,40 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
+          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -10698,13 +10626,11 @@
         </is>
       </c>
       <c r="O27" s="15">
-        <v>879988</v>
-      </c>
-      <c r="P27" s="15">
-        <v>-9826</v>
-      </c>
+        <v>703529</v>
+      </c>
+      <c r="P27" s="15"/>
       <c r="Q27" s="16">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R27" s="17" t="inlineStr">
         <is>
@@ -10713,7 +10639,7 @@
       </c>
       <c r="S27" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T27" s="15"/>
@@ -10725,25 +10651,25 @@
         <v>1</v>
       </c>
       <c r="Z27" s="20">
-        <v>131.98</v>
+        <v>78.99</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="19">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AE27" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
       </c>
       <c r="AH27" s="20">
-        <v>8.68</v>
+        <v>5.56</v>
       </c>
       <c r="AI27" s="16">
         <v>0.78</v>
@@ -10751,11 +10677,11 @@
       <c r="AJ27"/>
       <c r="AK27" s="13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AL27" s="19">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="AM27" s="13" t="inlineStr">
         <is>
@@ -10766,14 +10692,14 @@
       <c r="AO27" s="13"/>
       <c r="AP27"/>
       <c r="AQ27" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR27" s="19">
         <v>1</v>
       </c>
       <c r="AS27" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT27" s="13" t="inlineStr">
@@ -10788,12 +10714,12 @@
       </c>
       <c r="AV27" s="14" t="inlineStr">
         <is>
-          <t>郑州市 河南 450000 CN</t>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
         </is>
       </c>
       <c r="AW27" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX27" s="13"/>
@@ -10806,7 +10732,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD27" s="13"/>
+      <c r="BD27" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE27" s="13"/>
       <c r="BF27" s="13"/>
       <c r="BG27" s="13"/>
@@ -10814,47 +10744,47 @@
       <c r="BI27" s="23"/>
       <c r="BJ27" s="23" t="inlineStr">
         <is>
-          <t>1.9 kg</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="BK27" s="23" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
+          <t>250.00 g</t>
         </is>
       </c>
       <c r="BL27" s="23" t="inlineStr">
         <is>
-          <t>36 x 29 x 25 cm</t>
+          <t>4 x 4 x 8 cm</t>
         </is>
       </c>
       <c r="BM27" s="23" t="inlineStr">
         <is>
-          <t>36.00 x 29.00 x 25.00 cm</t>
+          <t>4.00 x 4.00 x 8.00 cm</t>
         </is>
       </c>
       <c r="BN27" s="23" t="inlineStr">
         <is>
-          <t>2.6 kg</t>
+          <t>2 kg</t>
         </is>
       </c>
       <c r="BO27" s="23" t="inlineStr">
         <is>
-          <t>2.60 kg</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BP27" s="23" t="inlineStr">
         <is>
-          <t>33.3 x 28.1 x 27.2 cm</t>
+          <t>32.1 x 30 x 22 cm</t>
         </is>
       </c>
       <c r="BQ27" s="23" t="inlineStr">
         <is>
-          <t>33.30 x 28.10 x 27.20 cm</t>
+          <t>32.10 x 30.00 x 22.00 cm</t>
         </is>
       </c>
       <c r="BR27" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10795,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -10878,23 +10808,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
+          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="M28" s="14"/>
@@ -10915,11 +10845,11 @@
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -10971,40 +10901,40 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
+          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -11018,7 +10948,7 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>703529</v>
+        <v>526465</v>
       </c>
       <c r="P29" s="15"/>
       <c r="Q29" s="16">
@@ -11031,7 +10961,7 @@
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T29" s="15"/>
@@ -11043,37 +10973,37 @@
         <v>1</v>
       </c>
       <c r="Z29" s="20">
-        <v>78.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE29" s="15">
         <v>0</v>
       </c>
       <c r="AF29" s="21">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
       </c>
       <c r="AH29" s="20">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="AI29" s="16">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
@@ -11091,7 +11021,7 @@
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>ANISE EDALS52</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
@@ -11101,17 +11031,17 @@
       </c>
       <c r="AU29" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV29" s="14" t="inlineStr">
         <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
+          <t>LONDONDERRY NORTHERN IRELAND BT48 7DE GB</t>
         </is>
       </c>
       <c r="AW29" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6</t>
         </is>
       </c>
       <c r="AX29" s="13"/>
@@ -11119,16 +11049,8 @@
       <c r="AZ29" s="13"/>
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD29" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC29" s="13"/>
+      <c r="BD29" s="13"/>
       <c r="BE29" s="13"/>
       <c r="BF29" s="13"/>
       <c r="BG29" s="13"/>
@@ -11136,49 +11058,25 @@
       <c r="BI29" s="23"/>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>2,72 kg</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>250.00 g</t>
+          <t>2.72 kg</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>4 x 4 x 8 cm</t>
-        </is>
-      </c>
-      <c r="BM29" s="23" t="inlineStr">
-        <is>
-          <t>4.00 x 4.00 x 8.00 cm</t>
-        </is>
-      </c>
-      <c r="BN29" s="23" t="inlineStr">
-        <is>
-          <t>2 kg</t>
-        </is>
-      </c>
-      <c r="BO29" s="23" t="inlineStr">
-        <is>
-          <t>2.00 kg</t>
-        </is>
-      </c>
-      <c r="BP29" s="23" t="inlineStr">
-        <is>
-          <t>32.1 x 30 x 22 cm</t>
-        </is>
-      </c>
-      <c r="BQ29" s="23" t="inlineStr">
-        <is>
-          <t>32.10 x 30.00 x 22.00 cm</t>
-        </is>
-      </c>
-      <c r="BR29" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>27,2L x 18,8l x 32,9H cm</t>
+        </is>
+      </c>
+      <c r="BM29" s="23"/>
+      <c r="BN29" s="23"/>
+      <c r="BO29" s="23"/>
+      <c r="BP29" s="23"/>
+      <c r="BQ29" s="23"/>
+      <c r="BR29" s="13"/>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
@@ -11187,7 +11085,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -11200,23 +11098,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
+          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M30" s="14"/>
@@ -11237,11 +11135,11 @@
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="AE30" s="15"/>
       <c r="AF30" s="21">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -11293,149 +11191,83 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO</t>
-        </is>
-      </c>
+      <c r="F31" s="14"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
-        </is>
-      </c>
-      <c r="M31" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O31" s="15">
-        <v>526465</v>
-      </c>
+          <t>B0GJS592V3</t>
+        </is>
+      </c>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="15"/>
       <c r="P31" s="15"/>
-      <c r="Q31" s="16">
-        <v>0</v>
-      </c>
-      <c r="R31" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S31" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="18"/>
       <c r="T31" s="15"/>
       <c r="U31" s="16"/>
       <c r="V31" s="15"/>
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
-      <c r="Y31" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="20">
-        <v>65.99</v>
-      </c>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="20"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>3</v>
-      </c>
-      <c r="AE31" s="15">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="AE31" s="15"/>
       <c r="AF31" s="21">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
       </c>
-      <c r="AH31" s="20">
-        <v>5.3</v>
-      </c>
+      <c r="AH31" s="20"/>
       <c r="AI31" s="16">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="AJ31"/>
-      <c r="AK31" s="13" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AL31" s="19">
-        <v>298</v>
-      </c>
-      <c r="AM31" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK31" s="13"/>
+      <c r="AL31" s="19"/>
+      <c r="AM31" s="13"/>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31"/>
-      <c r="AQ31" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR31" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS31" s="14" t="inlineStr">
-        <is>
-          <t>ANISE EDALS52</t>
-        </is>
-      </c>
-      <c r="AT31" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU31" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV31" s="14" t="inlineStr">
-        <is>
-          <t>LONDONDERRY NORTHERN IRELAND BT48 7DE GB</t>
-        </is>
-      </c>
-      <c r="AW31" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6</t>
-        </is>
-      </c>
+      <c r="AQ31" s="19"/>
+      <c r="AR31" s="19"/>
+      <c r="AS31" s="14"/>
+      <c r="AT31" s="13"/>
+      <c r="AU31" s="13"/>
+      <c r="AV31" s="14"/>
+      <c r="AW31" s="13"/>
       <c r="AX31" s="13"/>
       <c r="AY31" s="13"/>
       <c r="AZ31" s="13"/>
@@ -11448,21 +11280,9 @@
       <c r="BG31" s="13"/>
       <c r="BH31" s="14"/>
       <c r="BI31" s="23"/>
-      <c r="BJ31" s="23" t="inlineStr">
-        <is>
-          <t>2,72 kg</t>
-        </is>
-      </c>
-      <c r="BK31" s="23" t="inlineStr">
-        <is>
-          <t>2.72 kg</t>
-        </is>
-      </c>
-      <c r="BL31" s="23" t="inlineStr">
-        <is>
-          <t>27,2L x 18,8l x 32,9H cm</t>
-        </is>
-      </c>
+      <c r="BJ31" s="23"/>
+      <c r="BK31" s="23"/>
+      <c r="BL31" s="23"/>
       <c r="BM31" s="23"/>
       <c r="BN31" s="23"/>
       <c r="BO31" s="23"/>
@@ -11477,7 +11297,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GSZ8XVY3</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -11490,23 +11310,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
+          <t>Lubluelu Aspirapolvere Antiacari 3-in-1 per Materassi, Potente Aspirazione 18 kPa, Pulitore per Materassi contro Acari, Polve</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GSZ8XVY3?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GSZ8XVY3</t>
         </is>
       </c>
       <c r="M32" s="14"/>
@@ -11527,11 +11347,11 @@
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE32" s="15"/>
       <c r="AF32" s="21">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -11583,89 +11403,153 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Vehiwell</t>
+        </is>
+      </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.itundefined</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
-        </is>
-      </c>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="15"/>
+          <t>B0GTYZLWW3</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+        </is>
+      </c>
+      <c r="O33" s="15">
+        <v>878550</v>
+      </c>
       <c r="P33" s="15"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="18"/>
+      <c r="Q33" s="16">
+        <v>0</v>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>Aspirapolvere per futon</t>
+        </is>
+      </c>
+      <c r="S33" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="T33" s="15"/>
       <c r="U33" s="16"/>
       <c r="V33" s="15"/>
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="20"/>
+      <c r="Y33" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="20">
+        <v>89.99</v>
+      </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
-      <c r="AD33" s="19">
-        <v>28</v>
-      </c>
+      <c r="AD33" s="19"/>
       <c r="AE33" s="15"/>
-      <c r="AF33" s="21">
-        <v>3.6</v>
-      </c>
+      <c r="AF33" s="21"/>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
-      <c r="AH33" s="20"/>
+      <c r="AH33" s="20">
+        <v>5.21</v>
+      </c>
       <c r="AI33" s="16">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AJ33"/>
-      <c r="AK33" s="13"/>
-      <c r="AL33" s="19"/>
-      <c r="AM33" s="13"/>
+      <c r="AK33" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AL33" s="19">
+        <v>93</v>
+      </c>
+      <c r="AM33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
       <c r="AP33"/>
-      <c r="AQ33" s="19"/>
-      <c r="AR33" s="19"/>
-      <c r="AS33" s="14"/>
-      <c r="AT33" s="13"/>
-      <c r="AU33" s="13"/>
-      <c r="AV33" s="14"/>
-      <c r="AW33" s="13"/>
+      <c r="AQ33" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR33" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS33" s="14" t="inlineStr">
+        <is>
+          <t>DLLest</t>
+        </is>
+      </c>
+      <c r="AT33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU33" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV33" s="14" t="inlineStr">
+        <is>
+          <t>荆州市 湖北省 434021 CN</t>
+        </is>
+      </c>
+      <c r="AW33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU</t>
+        </is>
+      </c>
       <c r="AX33" s="13"/>
       <c r="AY33" s="13"/>
       <c r="AZ33" s="13"/>
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
-      <c r="BC33" s="13"/>
+      <c r="BC33" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD33" s="13"/>
       <c r="BE33" s="13"/>
       <c r="BF33" s="13"/>
@@ -11674,13 +11558,37 @@
       <c r="BI33" s="23"/>
       <c r="BJ33" s="23"/>
       <c r="BK33" s="23"/>
-      <c r="BL33" s="23"/>
+      <c r="BL33" s="23" t="inlineStr">
+        <is>
+          <t>34L x 28l x 22H cm</t>
+        </is>
+      </c>
       <c r="BM33" s="23"/>
-      <c r="BN33" s="23"/>
-      <c r="BO33" s="23"/>
-      <c r="BP33" s="23"/>
-      <c r="BQ33" s="23"/>
-      <c r="BR33" s="13"/>
+      <c r="BN33" s="23" t="inlineStr">
+        <is>
+          <t>2 kg</t>
+        </is>
+      </c>
+      <c r="BO33" s="23" t="inlineStr">
+        <is>
+          <t>2.00 kg</t>
+        </is>
+      </c>
+      <c r="BP33" s="23" t="inlineStr">
+        <is>
+          <t>34 x 28 x 22 cm</t>
+        </is>
+      </c>
+      <c r="BQ33" s="23" t="inlineStr">
+        <is>
+          <t>34.00 x 28.00 x 22.00 cm</t>
+        </is>
+      </c>
+      <c r="BR33" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
@@ -11689,7 +11597,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GSZ8XVY3</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -11702,23 +11610,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirapolvere Antiacari 3-in-1 per Materassi, Potente Aspirazione 18 kPa, Pulitore per Materassi contro Acari, Polve</t>
+          <t>Circlio 18 kPa Battimaterasso Antiacaro Senza Fili con Luce UV-C 254 nmsDoppio Contenitore della Polvere | Rimuove il 99% d</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GSZ8XVY3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H1HSF3G6?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GSZ8XVY3</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="M34" s="14"/>
@@ -11739,11 +11647,11 @@
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE34" s="15"/>
       <c r="AF34" s="21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -11795,40 +11703,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0H5K5QQZC</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell</t>
+          <t>VIHBRAI</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=VIHBRAI</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
+          <t>VIHBRAI Aspirapolvere senza fili per acari per materassi, con luce UV-C e potenza di aspirazione da 10 kPa, doppio contenitor</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H5K5QQZC?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0H5K5QQZC</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -11842,7 +11750,7 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>878550</v>
+        <v>577470</v>
       </c>
       <c r="P35" s="15"/>
       <c r="Q35" s="16">
@@ -11855,7 +11763,7 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T35" s="15"/>
@@ -11867,31 +11775,37 @@
         <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>89.99</v>
+        <v>36.99</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
-      <c r="AD35" s="19"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="21"/>
+      <c r="AD35" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE35" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="21">
+        <v>4</v>
+      </c>
       <c r="AG35" s="22">
         <v>0</v>
       </c>
       <c r="AH35" s="20">
-        <v>5.21</v>
+        <v>8.68</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -11902,14 +11816,14 @@
       <c r="AO35" s="13"/>
       <c r="AP35"/>
       <c r="AQ35" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR35" s="19">
         <v>1</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>DLLest</t>
+          <t>wzahqajw</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -11919,17 +11833,17 @@
       </c>
       <c r="AU35" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>荆州市 湖北省 434021 CN</t>
+          <t>NORTHERN IRELAND BT47 6DB GB</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ORNJ93EG8OSL</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
@@ -11937,11 +11851,7 @@
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
-      <c r="BC35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC35" s="13"/>
       <c r="BD35" s="13"/>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
@@ -11952,33 +11862,37 @@
       <c r="BK35" s="23"/>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>34L x 28l x 22H cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="23"/>
+          <t>28 x 28 x 31 cm</t>
+        </is>
+      </c>
+      <c r="BM35" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 28.00 x 31.00 cm</t>
+        </is>
+      </c>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>2 kg</t>
+          <t>1.8 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>1.80 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>34 x 28 x 22 cm</t>
+          <t>31 x 28 x 28 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>34.00 x 28.00 x 22.00 cm</t>
+          <t>31.00 x 28.00 x 28.00 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11903,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0HFN6BP5R</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -12002,23 +11916,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Circlio 18 kPa Battimaterasso Antiacaro Senza Fili con Luce UV-C 254 nmsDoppio Contenitore della Polvere | Rimuove il 99% d</t>
+          <t>Lubluelu Aspirapolvere Antiacaro 20kPa Senza Fili per Materassi UV-CsAspirapolvere per Materassi, Pulizia Profonda, fino al</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H1HSF3G6?psc=1</t>
+          <t>https://www.amazon.it/dp/B0HFN6BP5R?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0HFN6BP5R</t>
         </is>
       </c>
       <c r="M36" s="14"/>
@@ -12039,7 +11953,7 @@
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE36" s="15"/>
       <c r="AF36" s="21">
@@ -12087,312 +12001,6 @@
       <c r="BP36" s="23"/>
       <c r="BQ36" s="23"/>
       <c r="BR36" s="13"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>36</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>B0H5K5QQZC</t>
-        </is>
-      </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>VIHBRAI</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=VIHBRAI</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>VIHBRAI Aspirapolvere senza fili per acari per materassi, con luce UV-C e potenza di aspirazione da 10 kPa, doppio contenitor</t>
-        </is>
-      </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H5K5QQZC?psc=1</t>
-        </is>
-      </c>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L37" s="14" t="inlineStr">
-        <is>
-          <t>B0H5K5QQZC</t>
-        </is>
-      </c>
-      <c r="M37" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O37" s="15">
-        <v>577470</v>
-      </c>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="16">
-        <v>0</v>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S37" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="T37" s="15"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="20">
-        <v>36.99</v>
-      </c>
-      <c r="AA37"/>
-      <c r="AB37"/>
-      <c r="AC37" s="2"/>
-      <c r="AD37" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE37" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="20">
-        <v>8.68</v>
-      </c>
-      <c r="AI37" s="16">
-        <v>0.62</v>
-      </c>
-      <c r="AJ37"/>
-      <c r="AK37" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="AL37" s="19">
-        <v>69</v>
-      </c>
-      <c r="AM37" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN37" s="13"/>
-      <c r="AO37" s="13"/>
-      <c r="AP37"/>
-      <c r="AQ37" s="19">
-        <v>6</v>
-      </c>
-      <c r="AR37" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS37" s="14" t="inlineStr">
-        <is>
-          <t>wzahqajw</t>
-        </is>
-      </c>
-      <c r="AT37" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV37" s="14" t="inlineStr">
-        <is>
-          <t>NORTHERN IRELAND BT47 6DB GB</t>
-        </is>
-      </c>
-      <c r="AW37" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ORNJ93EG8OSL</t>
-        </is>
-      </c>
-      <c r="AX37" s="13"/>
-      <c r="AY37" s="13"/>
-      <c r="AZ37" s="13"/>
-      <c r="BA37" s="13"/>
-      <c r="BB37" s="13"/>
-      <c r="BC37" s="13"/>
-      <c r="BD37" s="13"/>
-      <c r="BE37" s="13"/>
-      <c r="BF37" s="13"/>
-      <c r="BG37" s="13"/>
-      <c r="BH37" s="14"/>
-      <c r="BI37" s="23"/>
-      <c r="BJ37" s="23"/>
-      <c r="BK37" s="23"/>
-      <c r="BL37" s="23" t="inlineStr">
-        <is>
-          <t>28 x 28 x 31 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>28.00 x 28.00 x 31.00 cm</t>
-        </is>
-      </c>
-      <c r="BN37" s="23" t="inlineStr">
-        <is>
-          <t>1.8 kg</t>
-        </is>
-      </c>
-      <c r="BO37" s="23" t="inlineStr">
-        <is>
-          <t>1.80 kg</t>
-        </is>
-      </c>
-      <c r="BP37" s="23" t="inlineStr">
-        <is>
-          <t>31 x 28 x 28 cm</t>
-        </is>
-      </c>
-      <c r="BQ37" s="23" t="inlineStr">
-        <is>
-          <t>31.00 x 28.00 x 28.00 cm</t>
-        </is>
-      </c>
-      <c r="BR37" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13">
-        <v>37</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>B0HFN6BP5R</t>
-        </is>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Aspirapolvere Antiacaro 20kPa Senza Fili per Materassi UV-CsAspirapolvere per Materassi, Pulizia Profonda, fino al</t>
-        </is>
-      </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0HFN6BP5R?psc=1</t>
-        </is>
-      </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L38" s="14" t="inlineStr">
-        <is>
-          <t>B0HFN6BP5R</t>
-        </is>
-      </c>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="19"/>
-      <c r="Z38" s="20"/>
-      <c r="AA38"/>
-      <c r="AB38"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="19">
-        <v>11</v>
-      </c>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="20"/>
-      <c r="AI38" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ38"/>
-      <c r="AK38" s="13"/>
-      <c r="AL38" s="19"/>
-      <c r="AM38" s="13"/>
-      <c r="AN38" s="13"/>
-      <c r="AO38" s="13"/>
-      <c r="AP38"/>
-      <c r="AQ38" s="19"/>
-      <c r="AR38" s="19"/>
-      <c r="AS38" s="14"/>
-      <c r="AT38" s="13"/>
-      <c r="AU38" s="13"/>
-      <c r="AV38" s="14"/>
-      <c r="AW38" s="13"/>
-      <c r="AX38" s="13"/>
-      <c r="AY38" s="13"/>
-      <c r="AZ38" s="13"/>
-      <c r="BA38" s="13"/>
-      <c r="BB38" s="13"/>
-      <c r="BC38" s="13"/>
-      <c r="BD38" s="13"/>
-      <c r="BE38" s="13"/>
-      <c r="BF38" s="13"/>
-      <c r="BG38" s="13"/>
-      <c r="BH38" s="14"/>
-      <c r="BI38" s="23"/>
-      <c r="BJ38" s="23"/>
-      <c r="BK38" s="23"/>
-      <c r="BL38" s="23"/>
-      <c r="BM38" s="23"/>
-      <c r="BN38" s="23"/>
-      <c r="BO38" s="23"/>
-      <c r="BP38" s="23"/>
-      <c r="BQ38" s="23"/>
-      <c r="BR38" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12547,117 +12155,104 @@
     <hyperlink ref="J21" r:id="rId147" tooltip="https://www.amazon.it/dp/B0F8HD3649?psc=1"/>
     <hyperlink ref="K21" r:id="rId148" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L21" r:id="rId149" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
-    <hyperlink ref="C22" r:id="rId150" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
+    <hyperlink ref="C22" r:id="rId150" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
     <hyperlink ref="G22" r:id="rId151" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J22" r:id="rId152" tooltip="https://www.amazon.it/dp/B0F8W81X7Y?psc=1"/>
-    <hyperlink ref="K22" r:id="rId153" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId154" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
-    <hyperlink ref="C23" r:id="rId155" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G23" r:id="rId156" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J23" r:id="rId157" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K23" r:id="rId158" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId159" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C24" r:id="rId160" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="G24" r:id="rId161" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId162" tooltip="https://www.amazon.it/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K24" r:id="rId163" tooltip="https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId164" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="M24" r:id="rId165" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N24" r:id="rId166"/>
-    <hyperlink ref="AW24" r:id="rId167" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1LBASE3VLPMEX"/>
-    <hyperlink ref="C25" r:id="rId168" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="G25" r:id="rId169" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J25" r:id="rId170" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K25" r:id="rId171" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId172" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="M25" r:id="rId173" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N25" r:id="rId174"/>
-    <hyperlink ref="AW25" r:id="rId175" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C26" r:id="rId176" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="G26" r:id="rId177" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J26" r:id="rId178" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
-    <hyperlink ref="K26" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId180" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="M26" r:id="rId181" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N26" r:id="rId182"/>
-    <hyperlink ref="AW26" r:id="rId183" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C27" r:id="rId184" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G27" r:id="rId185" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
-    <hyperlink ref="J27" r:id="rId186" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K27" r:id="rId187" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId188" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="J22" r:id="rId152" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K22" r:id="rId153" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId154" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="C23" r:id="rId155" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="G23" r:id="rId156" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J23" r:id="rId157" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K23" r:id="rId158" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId159" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="M23" r:id="rId160" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N23" r:id="rId161"/>
+    <hyperlink ref="AW23" r:id="rId162" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C24" r:id="rId163" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="G24" r:id="rId164" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J24" r:id="rId165" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
+    <hyperlink ref="K24" r:id="rId166" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId167" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="M24" r:id="rId168" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N24" r:id="rId169"/>
+    <hyperlink ref="AW24" r:id="rId170" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C25" r:id="rId171" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G25" r:id="rId172" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
+    <hyperlink ref="J25" r:id="rId173" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K25" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId175" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="M25" r:id="rId176" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N25" r:id="rId177"/>
+    <hyperlink ref="AW25" r:id="rId178" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
+    <hyperlink ref="C26" r:id="rId179" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="G26" r:id="rId180" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J26" r:id="rId181" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
+    <hyperlink ref="K26" r:id="rId182" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId183" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="C27" r:id="rId184" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="G27" r:id="rId185" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J27" r:id="rId186" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
+    <hyperlink ref="K27" r:id="rId187" tooltip="https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId188" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
     <hyperlink ref="M27" r:id="rId189" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N27" r:id="rId190"/>
-    <hyperlink ref="AW27" r:id="rId191" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
-    <hyperlink ref="C28" r:id="rId192" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="AW27" r:id="rId191" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C28" r:id="rId192" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
     <hyperlink ref="G28" r:id="rId193" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J28" r:id="rId194" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
-    <hyperlink ref="K28" r:id="rId195" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId196" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
-    <hyperlink ref="C29" r:id="rId197" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
-    <hyperlink ref="G29" r:id="rId198" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J29" r:id="rId199" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
-    <hyperlink ref="K29" r:id="rId200" tooltip="https://images-na.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId201" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="J28" r:id="rId194" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
+    <hyperlink ref="K28" r:id="rId195" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId196" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="C29" r:id="rId197" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="G29" r:id="rId198" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId199" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
+    <hyperlink ref="K29" r:id="rId200" tooltip="https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId201" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
     <hyperlink ref="M29" r:id="rId202" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N29" r:id="rId203"/>
-    <hyperlink ref="AW29" r:id="rId204" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C30" r:id="rId205" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="AW29" r:id="rId204" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6"/>
+    <hyperlink ref="C30" r:id="rId205" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
     <hyperlink ref="G30" r:id="rId206" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J30" r:id="rId207" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
-    <hyperlink ref="K30" r:id="rId208" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId209" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
-    <hyperlink ref="C31" r:id="rId210" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
-    <hyperlink ref="G31" r:id="rId211" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId212" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
-    <hyperlink ref="K31" r:id="rId213" tooltip="https://images-na.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId214" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
-    <hyperlink ref="M31" r:id="rId215" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N31" r:id="rId216"/>
-    <hyperlink ref="AW31" r:id="rId217" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6"/>
-    <hyperlink ref="C32" r:id="rId218" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="G32" r:id="rId219" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J32" r:id="rId220" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K32" r:id="rId221" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId222" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="C33" r:id="rId223" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
-    <hyperlink ref="G33" r:id="rId224" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J33" r:id="rId225" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
-    <hyperlink ref="K33" r:id="rId226" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId227" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
-    <hyperlink ref="C34" r:id="rId228" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
+    <hyperlink ref="J30" r:id="rId207" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K30" r:id="rId208" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId209" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="C31" r:id="rId210" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="G31" r:id="rId211" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J31" r:id="rId212" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
+    <hyperlink ref="K31" r:id="rId213" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId214" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="C32" r:id="rId215" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
+    <hyperlink ref="G32" r:id="rId216" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J32" r:id="rId217" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3?psc=1"/>
+    <hyperlink ref="K32" r:id="rId218" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId219" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
+    <hyperlink ref="C33" r:id="rId220" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="G33" r:id="rId221" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell"/>
+    <hyperlink ref="J33" r:id="rId222" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K33" r:id="rId223" tooltip="https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId224" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="M33" r:id="rId225" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N33" r:id="rId226"/>
+    <hyperlink ref="AW33" r:id="rId227" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU"/>
+    <hyperlink ref="C34" r:id="rId228" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
     <hyperlink ref="G34" r:id="rId229" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J34" r:id="rId230" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3?psc=1"/>
-    <hyperlink ref="K34" r:id="rId231" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId232" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
-    <hyperlink ref="C35" r:id="rId233" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
-    <hyperlink ref="G35" r:id="rId234" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell"/>
-    <hyperlink ref="J35" r:id="rId235" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K35" r:id="rId236" tooltip="https://images-na.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId237" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="J34" r:id="rId230" tooltip="https://www.amazon.it/dp/B0H1HSF3G6?psc=1"/>
+    <hyperlink ref="K34" r:id="rId231" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId232" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
+    <hyperlink ref="C35" r:id="rId233" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
+    <hyperlink ref="G35" r:id="rId234" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=VIHBRAI"/>
+    <hyperlink ref="J35" r:id="rId235" tooltip="https://www.amazon.it/dp/B0H5K5QQZC?psc=1"/>
+    <hyperlink ref="K35" r:id="rId236" tooltip="https://images-na.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId237" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
     <hyperlink ref="M35" r:id="rId238" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N35" r:id="rId239"/>
-    <hyperlink ref="AW35" r:id="rId240" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1F2NCGM6KYOZU"/>
-    <hyperlink ref="C36" r:id="rId241" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
+    <hyperlink ref="AW35" r:id="rId240" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ORNJ93EG8OSL"/>
+    <hyperlink ref="C36" r:id="rId241" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
     <hyperlink ref="G36" r:id="rId242" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J36" r:id="rId243" tooltip="https://www.amazon.it/dp/B0H1HSF3G6?psc=1"/>
-    <hyperlink ref="K36" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId245" tooltip="https://www.amazon.it/dp/B0H1HSF3G6"/>
-    <hyperlink ref="C37" r:id="rId246" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
-    <hyperlink ref="G37" r:id="rId247" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=VIHBRAI"/>
-    <hyperlink ref="J37" r:id="rId248" tooltip="https://www.amazon.it/dp/B0H5K5QQZC?psc=1"/>
-    <hyperlink ref="K37" r:id="rId249" tooltip="https://images-na.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId250" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
-    <hyperlink ref="M37" r:id="rId251" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N37" r:id="rId252"/>
-    <hyperlink ref="AW37" r:id="rId253" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ORNJ93EG8OSL"/>
-    <hyperlink ref="C38" r:id="rId254" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
-    <hyperlink ref="G38" r:id="rId255" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J38" r:id="rId256" tooltip="https://www.amazon.it/dp/B0HFN6BP5R?psc=1"/>
-    <hyperlink ref="K38" r:id="rId257" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId258" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
+    <hyperlink ref="J36" r:id="rId243" tooltip="https://www.amazon.it/dp/B0HFN6BP5R?psc=1"/>
+    <hyperlink ref="K36" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId245" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
   </hyperlinks>
-  <drawing r:id="rId259"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
@@ -13094,7 +12689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -13562,7 +13157,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>tengjidainzi</t>
+          <t>wzahqajw</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -13575,25 +13170,6 @@
       <c r="E23" s="15"/>
       <c r="F23" s="20"/>
       <c r="G23" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>wzahqajw</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <v>0</v>
-      </c>
-      <c r="C24" s="15">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="22">
         <v>0.0</v>
       </c>
     </row>
